--- a/data/invalid.xlsx
+++ b/data/invalid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6113f60f932799a7/1Evan/.eff_fron_spyder/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{D72D1906-9C93-401E-93C1-D4F2CBEF1668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3392D4D1-CEE9-4F2E-8A37-A87E3949532D}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{D72D1906-9C93-401E-93C1-D4F2CBEF1668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44F1C016-C810-418E-8B1A-29CB7C3345A0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40" yWindow="0" windowWidth="25560" windowHeight="13660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Investments" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Ticker</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>WXY</t>
+  </si>
+  <si>
+    <t>Curr Weight</t>
   </si>
 </sst>
 </file>
@@ -163,6 +166,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -453,15 +460,16 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.453125" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -471,8 +479,11 @@
       <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -483,7 +494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -494,7 +505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -505,7 +516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -516,7 +527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -527,24 +538,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
